--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>11.66</t>
+          <t>11.35</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>63.38</t>
+          <t>64.37</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>22.61</t>
+          <t>22.00</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>26.78</t>
+          <t>25.97</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>41.69</t>
+          <t>41.07</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1330.00</t>
+          <t>1316.01</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>87.40</t>
+          <t>86.51</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>18.24</t>
+          <t>18.17</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>11.34</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>64.37</t>
+          <t>62.18</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>22.00</t>
+          <t>22.51</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>25.97</t>
+          <t>25.86</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>41.07</t>
+          <t>40.90</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1316.01</t>
+          <t>1309.30</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>86.51</t>
+          <t>86.57</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>18.17</t>
+          <t>18.93</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>11.34</t>
+          <t>11.75</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>62.18</t>
+          <t>62.30</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>22.51</t>
+          <t>23.22</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>28.45</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>40.90</t>
+          <t>41.00</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1309.30</t>
+          <t>1290.88</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>86.57</t>
+          <t>85.88</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>18.93</t>
+          <t>19.08</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>11.75</t>
+          <t>11.35</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>62.30</t>
+          <t>59.75</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>23.22</t>
+          <t>22.61</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>28.45</t>
+          <t>28.54</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>41.00</t>
+          <t>41.57</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1290.88</t>
+          <t>1285.13</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>85.88</t>
+          <t>83.52</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>20.08</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>11.25</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>59.75</t>
+          <t>58.23</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>22.61</t>
+          <t>21.16</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>28.54</t>
+          <t>27.50</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>41.35</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1285.13</t>
+          <t>1275.16</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>83.52</t>
+          <t>84.00</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>20.08</t>
+          <t>19.45</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>11.25</t>
+          <t>11.34</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>58.23</t>
+          <t>58.26</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>21.16</t>
+          <t>20.91</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>27.50</t>
+          <t>26.95</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>41.83</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1275.16</t>
+          <t>1277.96</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>84.00</t>
+          <t>85.43</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>19.45</t>
+          <t>19.68</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>11.34</t>
+          <t>11.09</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>58.26</t>
+          <t>58.58</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>20.91</t>
+          <t>20.85</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>26.95</t>
+          <t>26.57</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>41.83</t>
+          <t>41.10</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1277.96</t>
+          <t>1272.75</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>85.43</t>
+          <t>84.30</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>19.68</t>
+          <t>19.96</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>11.09</t>
+          <t>11.04</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>58.58</t>
+          <t>59.98</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>20.85</t>
+          <t>21.81</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>26.57</t>
+          <t>27.16</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>41.10</t>
+          <t>40.92</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1272.75</t>
+          <t>1258.00</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>84.30</t>
+          <t>83.96</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>19.96</t>
+          <t>20.02</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>11.10</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>59.98</t>
+          <t>59.35</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>21.33</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>27.16</t>
+          <t>25.49</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>40.92</t>
+          <t>40.60</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1258.00</t>
+          <t>1266.98</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>83.96</t>
+          <t>84.97</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>20.02</t>
+          <t>19.70</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>11.10</t>
+          <t>11.17</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>59.35</t>
+          <t>59.98</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>21.33</t>
+          <t>21.44</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>25.49</t>
+          <t>25.76</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>40.60</t>
+          <t>40.59</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1266.98</t>
+          <t>1257.12</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>84.97</t>
+          <t>84.30</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>19.70</t>
+          <t>21.67</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>11.17</t>
+          <t>11.51</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>59.98</t>
+          <t>59.77</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>21.44</t>
+          <t>21.23</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>25.76</t>
+          <t>25.29</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>40.59</t>
+          <t>41.04</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1257.12</t>
+          <t>1252.57</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>84.30</t>
+          <t>85.22</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>21.67</t>
+          <t>21.04</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>11.51</t>
+          <t>11.34</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>59.77</t>
+          <t>59.15</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>21.23</t>
+          <t>21.08</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>25.29</t>
+          <t>25.00</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>41.04</t>
+          <t>40.82</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1252.57</t>
+          <t>1253.80</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>85.22</t>
+          <t>86.58</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>21.04</t>
+          <t>20.29</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>11.34</t>
+          <t>11.23</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>59.15</t>
+          <t>59.27</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>21.08</t>
+          <t>22.14</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>25.00</t>
+          <t>24.82</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.60</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1253.80</t>
+          <t>1251.24</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>86.58</t>
+          <t>85.85</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>20.29</t>
+          <t>19.87</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>11.23</t>
+          <t>11.06</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>59.27</t>
+          <t>58.13</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>22.14</t>
+          <t>21.00</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>24.82</t>
+          <t>23.69</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>40.60</t>
+          <t>40.69</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1251.24</t>
+          <t>1237.00</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>85.85</t>
+          <t>84.34</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>19.87</t>
+          <t>20.30</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>11.06</t>
+          <t>10.80</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>58.13</t>
+          <t>57.31</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>21.00</t>
+          <t>19.52</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>23.69</t>
+          <t>22.67</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>40.69</t>
+          <t>40.64</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1237.00</t>
+          <t>1243.88</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>84.34</t>
+          <t>83.35</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>20.30</t>
+          <t>20.08</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>10.80</t>
+          <t>10.71</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>57.31</t>
+          <t>56.93</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>19.52</t>
+          <t>19.66</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>22.67</t>
+          <t>23.20</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>40.64</t>
+          <t>41.26</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1243.88</t>
+          <t>1258.62</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>83.35</t>
+          <t>83.31</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>20.08</t>
+          <t>18.88</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>10.71</t>
+          <t>10.98</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>56.93</t>
+          <t>54.49</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>19.66</t>
+          <t>19.35</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>23.20</t>
+          <t>22.76</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>41.26</t>
+          <t>41.71</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1258.62</t>
+          <t>1255.79</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>83.31</t>
+          <t>81.72</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>18.88</t>
+          <t>19.10</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>10.98</t>
+          <t>10.95</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>54.49</t>
+          <t>54.80</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>19.35</t>
+          <t>19.65</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>22.76</t>
+          <t>23.96</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>41.71</t>
+          <t>41.42</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1255.79</t>
+          <t>1263.00</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>81.72</t>
+          <t>84.95</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>19.10</t>
+          <t>18.39</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>10.95</t>
+          <t>10.54</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>54.80</t>
+          <t>52.07</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>18.76</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>23.96</t>
+          <t>22.93</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>41.42</t>
+          <t>42.76</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1263.00</t>
+          <t>1288.00</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>84.95</t>
+          <t>84.60</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>18.39</t>
+          <t>17.89</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>10.54</t>
+          <t>10.82</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>52.07</t>
+          <t>51.80</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>18.76</t>
+          <t>18.46</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>42.76</t>
+          <t>42.80</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1288.00</t>
+          <t>1274.89</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>84.60</t>
+          <t>82.18</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>17.89</t>
+          <t>18.24</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>10.82</t>
+          <t>10.96</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>51.80</t>
+          <t>51.18</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>18.46</t>
+          <t>17.89</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>22.93</t>
+          <t>22.25</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>42.80</t>
+          <t>42.67</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1274.89</t>
+          <t>1286.00</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>82.18</t>
+          <t>81.44</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>18.24</t>
+          <t>17.90</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>10.96</t>
+          <t>10.41</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>51.18</t>
+          <t>49.56</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>17.89</t>
+          <t>16.76</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>22.25</t>
+          <t>21.72</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>42.66</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1286.00</t>
+          <t>1312.97</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>81.44</t>
+          <t>82.24</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>17.90</t>
+          <t>17.07</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>10.41</t>
+          <t>10.67</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>49.56</t>
+          <t>50.25</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>16.76</t>
+          <t>16.87</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>21.72</t>
+          <t>21.95</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>42.66</t>
+          <t>42.45</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1312.97</t>
+          <t>1329.00</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>82.24</t>
+          <t>82.72</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>17.07</t>
+          <t>17.99</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>10.67</t>
+          <t>10.83</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>50.25</t>
+          <t>48.84</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>16.87</t>
+          <t>16.67</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>22.13</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>42.45</t>
+          <t>43.05</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1329.00</t>
+          <t>1324.97</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>82.72</t>
+          <t>83.50</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>17.99</t>
+          <t>17.75</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>10.83</t>
+          <t>10.46</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>48.84</t>
+          <t>50.60</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>16.90</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>21.72</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>43.05</t>
+          <t>42.52</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1324.97</t>
+          <t>1331.88</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>83.50</t>
+          <t>82.60</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.67</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>10.46</t>
+          <t>10.59</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>50.60</t>
+          <t>50.55</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>16.90</t>
+          <t>16.80</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>21.72</t>
+          <t>21.85</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>42.52</t>
+          <t>42.28</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1331.88</t>
+          <t>1309.69</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>82.60</t>
+          <t>80.70</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>17.67</t>
+          <t>17.78</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>10.59</t>
+          <t>10.20</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>50.55</t>
+          <t>49.55</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>16.80</t>
+          <t>15.94</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>21.85</t>
+          <t>20.92</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>42.28</t>
+          <t>41.82</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1309.69</t>
+          <t>1318.49</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>80.70</t>
+          <t>80.02</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>17.78</t>
+          <t>16.79</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>10.20</t>
+          <t>10.22</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>50.07</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>15.94</t>
+          <t>16.03</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>20.92</t>
+          <t>20.74</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>41.82</t>
+          <t>41.77</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1318.49</t>
+          <t>1335.00</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>81.42</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>16.79</t>
+          <t>17.26</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>10.22</t>
+          <t>10.39</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>50.07</t>
+          <t>49.90</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>16.03</t>
+          <t>15.47</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>20.74</t>
+          <t>20.04</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>41.77</t>
+          <t>42.50</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1335.00</t>
+          <t>1349.98</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>81.42</t>
+          <t>82.40</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>17.26</t>
+          <t>16.79</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>10.39</t>
+          <t>10.27</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>49.90</t>
+          <t>48.18</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>15.47</t>
+          <t>15.08</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>20.04</t>
+          <t>19.67</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>42.50</t>
+          <t>42.99</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1349.98</t>
+          <t>1355.90</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>82.40</t>
+          <t>82.01</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>16.79</t>
+          <t>15.87</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>10.27</t>
+          <t>10.35</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>48.18</t>
+          <t>49.66</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>19.67</t>
+          <t>19.49</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>42.99</t>
+          <t>42.13</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1355.90</t>
+          <t>1330.75</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>82.01</t>
+          <t>82.74</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>15.87</t>
+          <t>16.53</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>10.35</t>
+          <t>11.39</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>49.66</t>
+          <t>47.65</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>15.08</t>
+          <t>14.49</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>19.49</t>
+          <t>18.91</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>42.13</t>
+          <t>42.94</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1330.75</t>
+          <t>1354.00</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>82.74</t>
+          <t>82.50</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>16.53</t>
+          <t>17.03</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>11.39</t>
+          <t>11.47</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>43.68</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>14.49</t>
+          <t>13.50</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>18.91</t>
+          <t>17.84</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>42.94</t>
+          <t>43.55</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1354.00</t>
+          <t>1392.05</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>82.50</t>
+          <t>81.65</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>17.03</t>
+          <t>16.53</t>
         </is>
       </c>
     </row>
